--- a/VerveStacks_POL_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{08287246-7A15-439B-B1CF-AFFBD44BB221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5B6F570B-B1FB-4DB6-9F9E-CD63D755C770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -311,9 +311,6 @@
     <t>life</t>
   </si>
   <si>
-    <t>g[_]*</t>
-  </si>
-  <si>
     <t>prc_capact</t>
   </si>
   <si>
@@ -375,6 +372,9 @@
   </si>
   <si>
     <t>UCE_min oil fleet utilization</t>
+  </si>
+  <si>
+    <t>g[_]*,distr*</t>
   </si>
   <si>
     <t>windon</t>
@@ -5475,7 +5475,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5DB1C8D-EB5A-4D10-853D-27F99E3FE25A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CE1ED2B-5328-42AC-99B3-E5AFD9F6E5CB}">
   <dimension ref="B2:AF942"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -23630,7 +23630,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{470A0878-41E9-46A9-B2D3-33C6D00B81BF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E4C54B-E4BB-40B7-A3F1-7D478CE71E6E}">
   <dimension ref="B9:L88"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -26511,7 +26511,7 @@
     </row>
     <row r="5" spans="1:38" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C5" t="s">
         <v>38</v>
@@ -26534,7 +26534,7 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C6" t="s">
         <v>7</v>
@@ -26567,7 +26567,7 @@
     </row>
     <row r="7" spans="1:38" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
         <v>7</v>
@@ -26795,7 +26795,7 @@
         <v>0.40616152968036529</v>
       </c>
       <c r="AF10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AG10" t="s">
         <v>23</v>
@@ -26830,7 +26830,7 @@
         <v>26</v>
       </c>
       <c r="U13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:38" x14ac:dyDescent="0.45">
@@ -26883,7 +26883,7 @@
         <v>Hydropower - large-scale unit,Solar photovoltaics - Large scale unit,Wind offshore,Wind onshore</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="U15" t="s">
         <v>59</v>
@@ -26906,7 +26906,7 @@
         <v>0</v>
       </c>
       <c r="AF15" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:38" x14ac:dyDescent="0.45">
@@ -27039,7 +27039,7 @@
         <v>42</v>
       </c>
       <c r="E27">
-        <v>0.03</v>
+        <v>0.1</v>
       </c>
       <c r="F27" t="str">
         <f>C27</f>
@@ -27054,18 +27054,18 @@
         <v>50</v>
       </c>
       <c r="G28" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B29" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E29">
         <v>8.76</v>
       </c>
       <c r="G29" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -27102,28 +27102,28 @@
         <v>124</v>
       </c>
       <c r="C10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D10" t="s">
         <v>64</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>65</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>66</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>67</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>68</v>
       </c>
-      <c r="H10" t="s">
+      <c r="I10" t="s">
         <v>69</v>
       </c>
-      <c r="I10" t="s">
+      <c r="J10" t="s">
         <v>70</v>
-      </c>
-      <c r="J10" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.45">
@@ -27162,7 +27162,7 @@
     </row>
     <row r="18" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B18" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -27170,16 +27170,16 @@
         <v>43</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>2</v>
       </c>
       <c r="D19" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E19" s="8" t="s">
         <v>73</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>74</v>
       </c>
       <c r="F19" s="8">
         <v>2025</v>
@@ -27204,7 +27204,7 @@
         <v>solar</v>
       </c>
       <c r="D20" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -27234,7 +27234,7 @@
         <v>wind*</v>
       </c>
       <c r="D21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -27264,7 +27264,7 @@
         <v>hydro</v>
       </c>
       <c r="D22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -27294,7 +27294,7 @@
         <v>nuclear</v>
       </c>
       <c r="D23" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -37333,7 +37333,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BEC8D27-AF42-43B2-907D-498F5CAB9488}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C5DC7CA-CF65-47CE-96C0-FB1015BC03A6}">
   <dimension ref="A1:I54"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -37355,7 +37355,7 @@
         <v>1509</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
         <v>14</v>
@@ -37367,7 +37367,7 @@
         <v>1515</v>
       </c>
       <c r="G4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H4" t="s">
         <v>2</v>

--- a/VerveStacks_POL_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_POL_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5B6F570B-B1FB-4DB6-9F9E-CD63D755C770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ACAE431-AF91-464E-ABCE-D2D814BDCD3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grids" sheetId="6" r:id="rId1"/>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6993" uniqueCount="1617">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7001" uniqueCount="1620">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -4984,6 +4984,15 @@
   </si>
   <si>
     <t>elc_won_POL_020</t>
+  </si>
+  <si>
+    <t>NCAP_START</t>
+  </si>
+  <si>
+    <t>-co2cap*</t>
+  </si>
+  <si>
+    <t>COAL</t>
   </si>
 </sst>
 </file>
@@ -27077,7 +27086,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{320A1887-1B0C-44A8-9658-90FD86FEE0A5}">
-  <dimension ref="A9:J23"/>
+  <dimension ref="A9:J30"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="6.59765625" bestFit="1" customWidth="1"/>
@@ -27311,6 +27320,39 @@
         <v>4</v>
       </c>
     </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="B28" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="B29" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" t="s">
+        <v>14</v>
+      </c>
+      <c r="D29" t="s">
+        <v>28</v>
+      </c>
+      <c r="E29" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="B30" t="s">
+        <v>1617</v>
+      </c>
+      <c r="C30" t="s">
+        <v>1618</v>
+      </c>
+      <c r="D30">
+        <v>2100</v>
+      </c>
+      <c r="E30" t="s">
+        <v>1619</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/VerveStacks_POL_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9B7645BA-3EB9-4205-A669-11CB6B94B215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{89F87456-3BD6-4428-9354-DB8A01624310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5523,7 +5523,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3CA7966-8180-4101-AA24-363EEAB86B0E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B86AD3B8-7666-4BC6-A810-8A88680A87EC}">
   <dimension ref="B2:AF957"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -23888,7 +23888,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1B0B2E0-600C-437B-9DD8-F96D9762BDE1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B890AE9A-E500-4770-B316-74854C269925}">
   <dimension ref="B9:L88"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -37591,7 +37591,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{620DA505-F34A-4386-94B7-FAA774BB6CC9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BC1A894-9EB0-4295-9A2A-054ECCAA1AC0}">
   <dimension ref="A1:I54"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F2EE28B5-B516-4E8F-B579-75D59145DC78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{91B012FA-F498-41A7-9F01-36494694C6E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5320,7 +5320,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{20728741-C909-CA16-EAD3-CD1ED82D13A9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{89B35224-15B6-8F1B-4BEB-EB854307CE05}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5375,7 +5375,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A085F38F-C891-2518-CCC1-2CB441510F1A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B26D5D77-8690-3737-F866-8ACC6D158071}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5430,7 +5430,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34E492A2-B2F9-1988-1306-E53E1E02D44E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{432CA85C-2157-0852-4F49-1548BF325481}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5781,7 +5781,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADAB26E6-47CF-4E06-9E62-B2D472D12580}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C9B79CD-4D77-4251-8C73-776A870E0A57}">
   <dimension ref="A1:AF957"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -24177,7 +24177,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BFF8CF6-3093-4BE9-8239-E4AE2546683D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{712AD5B5-0569-4680-865C-98B303380B16}">
   <dimension ref="A1:L88"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -37971,7 +37971,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E75D2B94-EE53-43DB-9145-C1F7B53AAA88}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2E4A5AF-C18A-4048-A0ED-446D3A8AD0CB}">
   <dimension ref="A1:I54"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
